--- a/dist/assets/BOs/Oranos.xlsx
+++ b/dist/assets/BOs/Oranos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50BF96A-1AED-4358-83A8-F82894287A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2E9C60-E400-4AC1-A8C7-637D4D66ACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1613,7 +1613,7 @@
     <t>https://www.youtube.com/watch?v=GZhVM3WpLeA</t>
   </si>
   <si>
-    <t>Oranos/Kronos - 6 Citizen Rush BO - By Chonikler IV</t>
+    <t>Oranos/Kronos - 6 Citizen Rush BO - By ChoniclerIV</t>
   </si>
 </sst>
 </file>
@@ -1624,11 +1624,18 @@
     <numFmt numFmtId="164" formatCode="[$-410]General"/>
     <numFmt numFmtId="165" formatCode="[$€-410]&quot; &quot;#,##0.00;[Red]&quot;-&quot;[$€-410]&quot; &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1913,23 +1920,22 @@
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1939,75 +1945,61 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="38" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="39" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="3" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Excel Built-in Hyperlink" xfId="3" xr:uid="{1E964D8A-50E3-4121-B4FE-FF6AF441516A}"/>
@@ -2236,164 +2228,150 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="15.6">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="13.8">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" ht="13.8">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="45" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="27" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.8">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="37"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" ht="13.8">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="37"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" ht="13.8">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="37"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" ht="13.8">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="37"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" ht="13.8">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.6">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
     </row>
     <row r="11" spans="1:4" ht="13.8">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="13.8">
-      <c r="A12" s="37"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="37"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="13.8">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="31"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
     </row>
     <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="40"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
+      <c r="A16" s="15"/>
     </row>
     <row r="17" spans="1:2" ht="15">
-      <c r="A17" s="40"/>
-      <c r="B17" s="36"/>
+      <c r="A17" s="15"/>
     </row>
     <row r="18" spans="1:2" ht="15">
-      <c r="A18" s="40"/>
-      <c r="B18" s="41"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="17"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="42"/>
-      <c r="B19" s="36"/>
+      <c r="A19" s="18"/>
     </row>
     <row r="20" spans="1:2" ht="15">
-      <c r="A20" s="41"/>
-      <c r="B20" s="36"/>
+      <c r="A20" s="17"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="42"/>
-      <c r="B21" s="36"/>
+      <c r="A21" s="18"/>
     </row>
     <row r="22" spans="1:2" ht="15">
-      <c r="A22" s="41"/>
-      <c r="B22" s="36"/>
+      <c r="A22" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2418,20 +2396,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="15.6">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="13.8">
       <c r="A3" s="1" t="s">
@@ -2522,12 +2500,12 @@
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" ht="15.6">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
     </row>
     <row r="13" spans="1:4" ht="13.8">
       <c r="A13" s="1"/>
@@ -2557,12 +2535,12 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.6">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
     </row>
     <row r="17" spans="1:4" ht="13.8">
       <c r="A17" s="1" t="s">
@@ -2592,10 +2570,10 @@
       <c r="D20" s="14"/>
     </row>
     <row r="21" spans="1:4" ht="13.2">
-      <c r="A21" s="31"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
     </row>
     <row r="22" spans="1:4" ht="15">
       <c r="A22" s="15" t="s">
@@ -2653,12 +2631,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="17.399999999999999">
       <c r="A2" s="25" t="s">
@@ -2757,12 +2735,12 @@
       <c r="D10" s="19"/>
     </row>
     <row r="11" spans="1:4" ht="15.6">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:4" ht="13.8">
       <c r="A12" s="19" t="s">
@@ -2928,12 +2906,12 @@
       <c r="D10" s="19"/>
     </row>
     <row r="11" spans="1:4" ht="15.6">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:4" ht="13.8">
       <c r="A12" s="19" t="s">
@@ -3000,12 +2978,12 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" ht="13.8">
       <c r="A2" s="20" t="s">
@@ -3096,12 +3074,12 @@
       <c r="D10" s="19"/>
     </row>
     <row r="11" spans="1:4" ht="15.6">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:4" ht="13.8">
       <c r="A12" s="19" t="s">
@@ -3253,20 +3231,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="15.6">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" ht="13.8">
       <c r="A3" s="1" t="s">
@@ -3341,12 +3319,12 @@
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="15.6">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
     </row>
     <row r="11" spans="1:4" ht="13.8">
       <c r="A11" s="1" t="s">
@@ -3367,12 +3345,12 @@
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="15.6">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" ht="13.8">
       <c r="A14" s="1" t="s">
@@ -3415,10 +3393,10 @@
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" ht="13.8">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="28"/>
+      <c r="B18" s="29"/>
       <c r="C18" s="1" t="s">
         <v>26</v>
       </c>
@@ -3482,12 +3460,12 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.6">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="11" t="s">
